--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-12-2025.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£11.89</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>£37.25</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£925.00</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
